--- a/artfynd/A 59601-2022 artfynd.xlsx
+++ b/artfynd/A 59601-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 59601-2022 artfynd.xlsx
+++ b/artfynd/A 59601-2022 artfynd.xlsx
@@ -1242,7 +1242,7 @@
         <v>0</v>
       </c>
       <c r="AE6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG6" t="b">
         <v>0</v>

--- a/artfynd/A 59601-2022 artfynd.xlsx
+++ b/artfynd/A 59601-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AY36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,57 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104590436</v>
+        <v>104925533</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Dals-Ed, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>313289.295039291</v>
+        <v>313426</v>
       </c>
       <c r="R2" t="n">
-        <v>6526151.231379387</v>
+        <v>6526102</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,40 +744,29 @@
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:11</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:11</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Christine Bryngelsson</t>
+          <t>Samuel Sjöberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Christine Bryngelsson, Samuel Sjöberg</t>
+          <t>Samuel Sjöberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -795,12 +776,7 @@
         <v>104925535</v>
       </c>
       <c r="B3" t="n">
-        <v>79433</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -833,10 +809,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>313349.7593487262</v>
+        <v>313349</v>
       </c>
       <c r="R3" t="n">
-        <v>6526123.420916464</v>
+        <v>6526123</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -866,19 +842,9 @@
           <t>2022-11-11</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,54 +871,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104925533</v>
+        <v>106012808</v>
       </c>
       <c r="B4" t="n">
-        <v>79433</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1049</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Dals-Ed, Dls</t>
+          <t>Holane, Dls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>313426.0704241383</v>
+        <v>313499</v>
       </c>
       <c r="R4" t="n">
-        <v>6526101.06706087</v>
+        <v>6526041</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -976,22 +936,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-01-12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-01-12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,27 +956,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Samuel Sjöberg</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Samuel Sjöberg</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104925531</v>
+        <v>106012774</v>
       </c>
       <c r="B5" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97780</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1034,44 +979,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>2389</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Purpurmylia</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Mylia taylorii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
+          <t>(Hook.) Gray</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Dals-Ed, Dls</t>
+          <t>Holane, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>313454.1799429343</v>
+        <v>313231</v>
       </c>
       <c r="R5" t="n">
-        <v>6526145.333894167</v>
+        <v>6526187</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1098,22 +1033,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-01-14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-01-14</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>2 närliggande lokaler med purpurmylia</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,72 +1058,57 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Samuel Sjöberg</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Samuel Sjöberg</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104925530</v>
+        <v>106012775</v>
       </c>
       <c r="B6" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97780</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4361</v>
+        <v>2389</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Purpurmylia</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Mylia taylorii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
+          <t>(Hook.) Gray</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Dals-Ed, Dls</t>
+          <t>Holane, Dls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>313454.1799429343</v>
+        <v>313191</v>
       </c>
       <c r="R6" t="n">
-        <v>6526145.333894167</v>
+        <v>6526184</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1220,29 +1135,19 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-01-14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-01-14</t>
         </is>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="b">
         <v>0</v>
@@ -1250,27 +1155,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Samuel Sjöberg</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Samuel Sjöberg</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104925526</v>
+        <v>106012748</v>
       </c>
       <c r="B7" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1278,47 +1178,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>2569</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Dals-Ed, Dls</t>
+          <t>Holane, Dls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>313240.099229799</v>
+        <v>313248</v>
       </c>
       <c r="R7" t="n">
-        <v>6526165.017395972</v>
+        <v>6526190</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1342,22 +1232,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-01-14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-01-14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1372,27 +1252,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Samuel Sjöberg</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Samuel Sjöberg</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104925534</v>
+        <v>106012749</v>
       </c>
       <c r="B8" t="n">
-        <v>73631</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1400,38 +1275,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6426</v>
+        <v>2569</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Dals-Ed, Dls</t>
+          <t>Holane, Dls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>313426.0704241383</v>
+        <v>313216</v>
       </c>
       <c r="R8" t="n">
-        <v>6526101.06706087</v>
+        <v>6526103</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1455,22 +1329,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-01-14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-01-14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1485,27 +1349,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Samuel Sjöberg</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Samuel Sjöberg</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>104925528</v>
+        <v>106012750</v>
       </c>
       <c r="B9" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1513,47 +1372,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>2569</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Dals-Ed, Dls</t>
+          <t>Holane, Dls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>313185.1360542607</v>
+        <v>313287</v>
       </c>
       <c r="R9" t="n">
-        <v>6526188.415495608</v>
+        <v>6526156</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1577,22 +1426,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-01-14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-01-14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1607,27 +1446,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Samuel Sjöberg</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Samuel Sjöberg</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>106012748</v>
+        <v>106012751</v>
       </c>
       <c r="B10" t="n">
-        <v>94838</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1659,10 +1493,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>313248.0618464834</v>
+        <v>313321</v>
       </c>
       <c r="R10" t="n">
-        <v>6526190.036953111</v>
+        <v>6526155</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1692,19 +1526,9 @@
           <t>2023-01-14</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-01-14</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1731,15 +1555,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>106012751</v>
+        <v>106012752</v>
       </c>
       <c r="B11" t="n">
-        <v>94838</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1771,10 +1590,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>313321.1548446738</v>
+        <v>313402</v>
       </c>
       <c r="R11" t="n">
-        <v>6526154.875238969</v>
+        <v>6526174</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1804,19 +1623,9 @@
           <t>2023-01-14</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-01-14</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1843,37 +1652,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>106012765</v>
+        <v>106012754</v>
       </c>
       <c r="B12" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1883,10 +1687,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>313264.9690796112</v>
+        <v>313247</v>
       </c>
       <c r="R12" t="n">
-        <v>6526195.959070037</v>
+        <v>6526169</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1916,24 +1720,9 @@
           <t>2023-01-14</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-01-14</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Läte</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1960,15 +1749,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>106012759</v>
+        <v>106012755</v>
       </c>
       <c r="B13" t="n">
-        <v>94838</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2000,10 +1784,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>313177.3056867764</v>
+        <v>313231</v>
       </c>
       <c r="R13" t="n">
-        <v>6526176.869747621</v>
+        <v>6526187</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2033,19 +1817,9 @@
           <t>2023-01-14</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-01-14</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2072,15 +1846,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>106012725</v>
+        <v>106012756</v>
       </c>
       <c r="B14" t="n">
-        <v>93054</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2088,21 +1857,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2810</v>
+        <v>2569</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2112,10 +1881,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>313455.8643556142</v>
+        <v>313220</v>
       </c>
       <c r="R14" t="n">
-        <v>6526115.699830489</v>
+        <v>6526199</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2145,19 +1914,9 @@
           <t>2023-01-14</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-01-14</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2184,15 +1943,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>106012750</v>
+        <v>106012757</v>
       </c>
       <c r="B15" t="n">
-        <v>94838</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2224,10 +1978,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>313287.4724556376</v>
+        <v>313191</v>
       </c>
       <c r="R15" t="n">
-        <v>6526156.504204579</v>
+        <v>6526184</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2257,19 +2011,9 @@
           <t>2023-01-14</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-01-14</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2296,15 +2040,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>106012774</v>
+        <v>106012758</v>
       </c>
       <c r="B16" t="n">
-        <v>95187</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2312,21 +2051,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2389</v>
+        <v>2569</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Purpurmylia</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Mylia taylorii</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hook.) Gray</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2336,10 +2075,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>313230.8115509443</v>
+        <v>313195</v>
       </c>
       <c r="R16" t="n">
-        <v>6526187.760740305</v>
+        <v>6526187</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2369,24 +2108,9 @@
           <t>2023-01-14</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-01-14</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>2 närliggande lokaler med purpurmylia</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2413,15 +2137,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>106012730</v>
+        <v>106012759</v>
       </c>
       <c r="B17" t="n">
-        <v>93054</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2429,21 +2148,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2810</v>
+        <v>2569</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2453,10 +2172,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>313224.575660389</v>
+        <v>313177</v>
       </c>
       <c r="R17" t="n">
-        <v>6526198.43171162</v>
+        <v>6526177</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2486,19 +2205,9 @@
           <t>2023-01-14</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-01-14</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2525,15 +2234,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>106012785</v>
+        <v>106012719</v>
       </c>
       <c r="B18" t="n">
-        <v>73631</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2541,21 +2245,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6426</v>
+        <v>2810</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2565,10 +2269,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>313224.7184465452</v>
+        <v>313282</v>
       </c>
       <c r="R18" t="n">
-        <v>6526190.647860134</v>
+        <v>6526143</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2598,19 +2302,9 @@
           <t>2023-01-14</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-01-14</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2637,15 +2331,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>106012733</v>
+        <v>106012721</v>
       </c>
       <c r="B19" t="n">
-        <v>93054</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2677,10 +2366,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>313177.3056867764</v>
+        <v>313350</v>
       </c>
       <c r="R19" t="n">
-        <v>6526176.869747621</v>
+        <v>6526165</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2710,19 +2399,9 @@
           <t>2023-01-14</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-01-14</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2749,15 +2428,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>106012732</v>
+        <v>106012723</v>
       </c>
       <c r="B20" t="n">
-        <v>93054</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2789,10 +2463,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>313201.0570970094</v>
+        <v>313401</v>
       </c>
       <c r="R20" t="n">
-        <v>6526195.422000793</v>
+        <v>6526183</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2822,19 +2496,9 @@
           <t>2023-01-14</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-01-14</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2861,15 +2525,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>106012755</v>
+        <v>106012725</v>
       </c>
       <c r="B21" t="n">
-        <v>94838</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2877,21 +2536,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2569</v>
+        <v>2810</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2901,10 +2560,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>313230.8115509443</v>
+        <v>313456</v>
       </c>
       <c r="R21" t="n">
-        <v>6526187.760740305</v>
+        <v>6526115</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2934,19 +2593,9 @@
           <t>2023-01-14</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2023-01-14</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2973,37 +2622,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>106012768</v>
+        <v>106012730</v>
       </c>
       <c r="B22" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3013,10 +2657,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>313183.899424836</v>
+        <v>313225</v>
       </c>
       <c r="R22" t="n">
-        <v>6526184.32762463</v>
+        <v>6526199</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -3046,24 +2690,9 @@
           <t>2023-01-14</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2023-01-14</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3090,15 +2719,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>106012758</v>
+        <v>106012732</v>
       </c>
       <c r="B23" t="n">
-        <v>94838</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3106,21 +2730,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2569</v>
+        <v>2810</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3130,10 +2754,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>313194.9565673504</v>
+        <v>313201</v>
       </c>
       <c r="R23" t="n">
-        <v>6526187.421790514</v>
+        <v>6526195</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3163,19 +2787,9 @@
           <t>2023-01-14</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2023-01-14</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3202,15 +2816,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>106012786</v>
+        <v>106012733</v>
       </c>
       <c r="B24" t="n">
-        <v>73631</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3218,21 +2827,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6426</v>
+        <v>2810</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3242,10 +2851,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>313178.1593339094</v>
+        <v>313177</v>
       </c>
       <c r="R24" t="n">
-        <v>6526162.31136171</v>
+        <v>6526177</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3275,19 +2884,9 @@
           <t>2023-01-14</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2023-01-14</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3314,15 +2913,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>106012757</v>
+        <v>106012735</v>
       </c>
       <c r="B25" t="n">
-        <v>94838</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3330,21 +2924,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2569</v>
+        <v>2810</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3354,10 +2948,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>313191.1790747097</v>
+        <v>313503</v>
       </c>
       <c r="R25" t="n">
-        <v>6526184.493803452</v>
+        <v>6526078</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3384,22 +2978,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2023-01-14</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-01-12</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2023-01-14</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-01-12</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3426,50 +3010,55 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>106012775</v>
+        <v>104925530</v>
       </c>
       <c r="B26" t="n">
-        <v>95187</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2389</v>
+        <v>4361</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Purpurmylia</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Mylia taylorii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hook.) Gray</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Holane, Dls</t>
+          <t>Dals-Ed, Dls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>313191.1790747097</v>
+        <v>313454</v>
       </c>
       <c r="R26" t="n">
-        <v>6526184.493803452</v>
+        <v>6526146</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3496,29 +3085,19 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2023-01-14</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-11</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2023-01-14</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-11</t>
         </is>
       </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG26" t="b">
         <v>0</v>
@@ -3526,62 +3105,67 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Samuel Sjöberg</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Samuel Sjöberg</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>106012721</v>
+        <v>104925531</v>
       </c>
       <c r="B27" t="n">
-        <v>93054</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2810</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Holane, Dls</t>
+          <t>Dals-Ed, Dls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>313350.2305590122</v>
+        <v>313454</v>
       </c>
       <c r="R27" t="n">
-        <v>6526165.394009823</v>
+        <v>6526146</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3608,22 +3192,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2023-01-14</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-11</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2023-01-14</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-11</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3638,27 +3212,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Samuel Sjöberg</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Samuel Sjöberg</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>106012735</v>
+        <v>104591658</v>
       </c>
       <c r="B28" t="n">
-        <v>93054</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3666,37 +3235,40 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2810</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Holane, Dls</t>
+          <t>Dals-Ed, Dls</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>313503.393701887</v>
+        <v>313187</v>
       </c>
       <c r="R28" t="n">
-        <v>6526078.147303712</v>
+        <v>6526197</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3720,22 +3292,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2023-01-12</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-11</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2023-01-12</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-11</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3744,33 +3306,29 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Christine Bryngelsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Christine Bryngelsson, Samuel Sjöberg</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>106012754</v>
+        <v>104925526</v>
       </c>
       <c r="B29" t="n">
-        <v>94838</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3778,37 +3336,47 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2569</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Holane, Dls</t>
+          <t>Dals-Ed, Dls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>313247.0358820772</v>
+        <v>313241</v>
       </c>
       <c r="R29" t="n">
-        <v>6526168.829541453</v>
+        <v>6526164</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3832,22 +3400,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2023-01-14</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-11</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2023-01-14</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-11</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3862,27 +3420,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Samuel Sjöberg</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Samuel Sjöberg</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>106012756</v>
+        <v>104925528</v>
       </c>
       <c r="B30" t="n">
-        <v>94838</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3890,37 +3443,47 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2569</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Holane, Dls</t>
+          <t>Dals-Ed, Dls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>313219.9620495601</v>
+        <v>313185</v>
       </c>
       <c r="R30" t="n">
-        <v>6526199.691863541</v>
+        <v>6526188</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3944,22 +3507,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2023-01-14</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-11</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2023-01-14</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-11</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3974,65 +3527,61 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Samuel Sjöberg</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Samuel Sjöberg</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>106012719</v>
+        <v>104925534</v>
       </c>
       <c r="B31" t="n">
-        <v>93054</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2810</v>
+        <v>6426</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Holane, Dls</t>
+          <t>Dals-Ed, Dls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>313282.6264077997</v>
+        <v>313426</v>
       </c>
       <c r="R31" t="n">
-        <v>6526142.221492841</v>
+        <v>6526102</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4056,22 +3605,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2023-01-14</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-11</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2023-01-14</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-11</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4086,68 +3625,60 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Samuel Sjöberg</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Samuel Sjöberg</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>104591658</v>
+        <v>106012785</v>
       </c>
       <c r="B32" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>6426</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Dals-Ed, Dls</t>
+          <t>Holane, Dls</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>313187.0660890036</v>
+        <v>313225</v>
       </c>
       <c r="R32" t="n">
-        <v>6526196.099050318</v>
+        <v>6526191</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4171,22 +3702,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-01-14</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-01-14</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4195,22 +3716,434 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>106012786</v>
+      </c>
+      <c r="B33" t="n">
+        <v>75428</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Holane, Dls</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>313178</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6526162</v>
+      </c>
+      <c r="S33" t="n">
+        <v>20</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Töftedal</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2023-01-14</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2023-01-14</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>106012765</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Holane, Dls</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>313265</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6526196</v>
+      </c>
+      <c r="S34" t="n">
+        <v>20</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Töftedal</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2023-01-14</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2023-01-14</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Läte</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>106012768</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Holane, Dls</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>313184</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6526184</v>
+      </c>
+      <c r="S35" t="n">
+        <v>20</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Töftedal</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2023-01-14</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2023-01-14</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Hack</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>104590436</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Dals-Ed, Dls</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>313289</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6526151</v>
+      </c>
+      <c r="S36" t="n">
+        <v>25</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Töftedal</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2022-11-11</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2022-11-11</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
           <t>Christine Bryngelsson</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
+      <c r="AX36" t="inlineStr">
         <is>
           <t>Christine Bryngelsson, Samuel Sjöberg</t>
         </is>
       </c>
-      <c r="AY32" t="inlineStr"/>
+      <c r="AY36" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 59601-2022 artfynd.xlsx
+++ b/artfynd/A 59601-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY36"/>
+  <dimension ref="A1:AZ36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104925533</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -868,6 +878,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104925535</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -965,6 +980,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106012808</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1067,6 +1087,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106012774</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1164,6 +1189,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106012775</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1261,6 +1291,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106012748</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1358,6 +1393,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106012749</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1455,6 +1495,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106012750</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1552,6 +1597,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106012751</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1649,6 +1699,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106012752</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1746,6 +1801,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106012754</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1843,6 +1903,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106012755</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1940,6 +2005,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106012756</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2037,6 +2107,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106012757</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2134,6 +2209,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106012758</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2231,6 +2311,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106012759</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2328,6 +2413,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106012719</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2425,6 +2515,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106012721</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2522,6 +2617,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106012723</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2619,6 +2719,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106012725</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2716,6 +2821,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106012730</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2813,6 +2923,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106012732</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2910,6 +3025,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106012733</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3007,6 +3127,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106012735</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3114,6 +3239,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104925530</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3221,6 +3351,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104925531</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3322,6 +3457,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104591658</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3429,6 +3569,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104925526</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3536,6 +3681,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104925528</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3634,6 +3784,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104925534</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3731,6 +3886,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106012785</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3828,6 +3988,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106012786</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3930,6 +4095,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106012765</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4032,6 +4202,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106012768</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4144,8 +4319,50 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104590436</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>